--- a/lab4/Лист Microsoft Excel.xlsx
+++ b/lab4/Лист Microsoft Excel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\OPD\lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140D8D15-DF2A-4FE4-8C68-9C1DBF9861E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="160">
   <si>
     <t>Адрес</t>
   </si>
@@ -502,12 +503,15 @@
   </si>
   <si>
     <t>Переход в 6D7 если &lt;= -2955</t>
+  </si>
+  <si>
+    <t>0EF -&gt; AC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -672,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -719,22 +723,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -748,12 +740,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1094,26 +1080,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" customWidth="1"/>
-    <col min="6" max="6" width="3.140625" customWidth="1"/>
-    <col min="7" max="7" width="33.5703125" customWidth="1"/>
-    <col min="8" max="9" width="1.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" customWidth="1"/>
-    <col min="14" max="14" width="33.42578125" customWidth="1"/>
-    <col min="15" max="15" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.453125" customWidth="1"/>
+    <col min="6" max="6" width="3.1796875" customWidth="1"/>
+    <col min="7" max="7" width="33.54296875" customWidth="1"/>
+    <col min="8" max="9" width="1.81640625" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="13" max="13" width="15.1796875" customWidth="1"/>
+    <col min="14" max="14" width="33.453125" customWidth="1"/>
+    <col min="15" max="15" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1150,29 +1136,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="2" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="17">
         <v>200</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="3"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="19" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="2" t="s">
@@ -1184,100 +1170,100 @@
       <c r="O2" s="9"/>
       <c r="P2" s="8"/>
     </row>
-    <row r="3" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="3"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="36" t="s">
+      <c r="N3" s="30" t="s">
         <v>32</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+    <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="32" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="3"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="31" t="s">
+      <c r="K4" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="27" t="s">
         <v>140</v>
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="17">
         <v>700</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="3"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="19" t="s">
         <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
@@ -1288,95 +1274,95 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="3"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="30"/>
+      <c r="N6" s="24"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+    <row r="7" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="3"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="30" t="s">
+      <c r="N7" s="24" t="s">
         <v>158</v>
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="17">
         <v>800</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="3"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="19">
         <v>500</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -1387,29 +1373,29 @@
       </c>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+    <row r="9" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="3"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="17">
         <v>500</v>
       </c>
       <c r="M9" s="2" t="s">
@@ -1420,11 +1406,11 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="37" t="s">
         <v>55</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -1433,18 +1419,18 @@
       <c r="D10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="5"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="17" t="s">
         <v>115</v>
       </c>
       <c r="M10" s="2" t="s">
@@ -1455,11 +1441,11 @@
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+    <row r="11" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="32" t="s">
         <v>57</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -1468,18 +1454,18 @@
       <c r="D11" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="3"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="L11" s="26" t="s">
+      <c r="L11" s="17" t="s">
         <v>76</v>
       </c>
       <c r="M11" s="2" t="s">
@@ -1490,29 +1476,29 @@
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="17" t="s">
         <v>118</v>
       </c>
       <c r="M12" s="2" t="s">
@@ -1523,64 +1509,64 @@
       </c>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+    <row r="13" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="3"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="17" t="s">
         <v>120</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="19" t="s">
         <v>138</v>
       </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
       <c r="H14" s="3"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="17" t="s">
         <v>122</v>
       </c>
       <c r="M14" s="2" t="s">
@@ -1591,31 +1577,31 @@
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+    <row r="15" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="3"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="27" t="s">
+      <c r="K15" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="L15" s="26" t="s">
+      <c r="L15" s="17" t="s">
         <v>124</v>
       </c>
       <c r="M15" s="2" t="s">
@@ -1626,11 +1612,11 @@
       </c>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="37" t="s">
         <v>65</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -1639,18 +1625,18 @@
       <c r="D16" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="3"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="L16" s="26" t="s">
+      <c r="L16" s="17" t="s">
         <v>126</v>
       </c>
       <c r="M16" s="2"/>
@@ -1659,11 +1645,11 @@
       </c>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="17" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="32" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="15" t="s">
@@ -1672,18 +1658,18 @@
       <c r="D17" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="L17" s="19" t="s">
         <v>128</v>
       </c>
       <c r="M17" s="2"/>
@@ -1692,56 +1678,56 @@
       </c>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+    <row r="18" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
       <c r="M18" s="2"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
+    <row r="19" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="23" t="s">
+      <c r="K19" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="L19" s="23" t="s">
+      <c r="L19" s="19" t="s">
         <v>141</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -1750,111 +1736,111 @@
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+    <row r="20" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="23" t="s">
+      <c r="K20" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="L20" s="23" t="s">
+      <c r="L20" s="19" t="s">
         <v>143</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
+    <row r="21" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="19" t="s">
         <v>143</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+    <row r="22" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
       <c r="M22" s="2"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
+    <row r="23" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1866,11 +1852,11 @@
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+    <row r="24" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="37" t="s">
         <v>78</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1882,8 +1868,8 @@
       <c r="E24" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -1893,106 +1879,106 @@
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+    <row r="25" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+    <row r="26" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="O26" s="7"/>
     </row>
-    <row r="27" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+    <row r="27" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="O27" s="7"/>
     </row>
-    <row r="28" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
+    <row r="28" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+    <row r="29" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
+    <row r="30" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2003,9 +1989,9 @@
       <c r="J30" s="2"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
+    <row r="31" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2016,9 +2002,9 @@
       <c r="J31" s="2"/>
       <c r="O31" s="7"/>
     </row>
-    <row r="32" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
+    <row r="32" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2033,9 +2019,9 @@
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
+    <row r="33" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -2050,9 +2036,9 @@
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -2067,9 +2053,9 @@
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -2084,9 +2070,9 @@
       <c r="N35" s="7"/>
       <c r="O35" s="7"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -2101,9 +2087,9 @@
       <c r="N36" s="7"/>
       <c r="O36" s="7"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -2118,9 +2104,9 @@
       <c r="N37" s="7"/>
       <c r="O37" s="7"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -2135,9 +2121,9 @@
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -2152,9 +2138,9 @@
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -2169,9 +2155,9 @@
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -2186,9 +2172,9 @@
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -2203,9 +2189,9 @@
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -2220,9 +2206,9 @@
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -2237,9 +2223,9 @@
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -2254,67 +2240,67 @@
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
     </row>

--- a/lab4/Лист Microsoft Excel.xlsx
+++ b/lab4/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140D8D15-DF2A-4FE4-8C68-9C1DBF9861E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A4F32E-6425-475E-8EC9-D7B7B0869007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
